--- a/data/dividends_info_20260519.xlsx
+++ b/data/dividends_info_20260519.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>51.83000183105469</v>
+        <v>52.15000152587891</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1736446012357175</v>
+        <v>0.1725790937040307</v>
       </c>
       <c r="J2" t="n">
         <v>300</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>55.04999923706055</v>
+        <v>53.79999923706055</v>
       </c>
       <c r="I3" t="n">
-        <v>1.271571316441997</v>
+        <v>1.301115260086843</v>
       </c>
       <c r="J3" t="n">
         <v>279</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.399999618530273</v>
+        <v>9.5</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6382978982437579</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="J4" t="n">
         <v>209</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>51.83000183105469</v>
+        <v>52.15000152587891</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1736446012357175</v>
+        <v>0.1725790937040307</v>
       </c>
       <c r="J6" t="n">
         <v>209</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.039999961853027</v>
+        <v>2.029999971389771</v>
       </c>
       <c r="I7" t="n">
-        <v>3.774509874503002</v>
+        <v>3.79310350173476</v>
       </c>
       <c r="J7" t="n">
         <v>188</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23.98500061035156</v>
+        <v>23.86000061035156</v>
       </c>
       <c r="I8" t="n">
-        <v>1.12570353608193</v>
+        <v>1.131600976920603</v>
       </c>
       <c r="J8" t="n">
         <v>188</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.730000019073486</v>
+        <v>5.570000171661377</v>
       </c>
       <c r="I9" t="n">
-        <v>3.490401384542038</v>
+        <v>3.590664162230099</v>
       </c>
       <c r="J9" t="n">
         <v>181</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6.599999904632568</v>
+        <v>6.900000095367432</v>
       </c>
       <c r="I10" t="n">
-        <v>0.909090922226919</v>
+        <v>0.8695652053727246</v>
       </c>
       <c r="J10" t="n">
         <v>153</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.099999904632568</v>
+        <v>5.400000095367432</v>
       </c>
       <c r="I12" t="n">
-        <v>0.980392175195585</v>
+        <v>0.925925909573486</v>
       </c>
       <c r="J12" t="n">
         <v>139</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>23.97999954223633</v>
+        <v>23.86000061035156</v>
       </c>
       <c r="I14" t="n">
-        <v>1.125938303395065</v>
+        <v>1.131600976920603</v>
       </c>
       <c r="J14" t="n">
         <v>125</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>51.83000183105469</v>
+        <v>52.15000152587891</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1736446012357175</v>
+        <v>0.1725790937040307</v>
       </c>
       <c r="J15" t="n">
         <v>125</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>4.409999847412109</v>
+        <v>4.489999771118164</v>
       </c>
       <c r="I16" t="n">
-        <v>6.802721323812448</v>
+        <v>6.681514817210997</v>
       </c>
       <c r="J16" t="n">
         <v>118</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.889999866485596</v>
+        <v>5.809999942779541</v>
       </c>
       <c r="I19" t="n">
-        <v>4.244482269388714</v>
+        <v>4.302926032050844</v>
       </c>
       <c r="J19" t="n">
         <v>69</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>9.631999969482422</v>
+        <v>9.557999610900879</v>
       </c>
       <c r="I20" t="n">
-        <v>2.699335556725206</v>
+        <v>2.720234469391174</v>
       </c>
       <c r="J20" t="n">
         <v>62</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>15.34000015258789</v>
+        <v>14.89999961853027</v>
       </c>
       <c r="I21" t="n">
-        <v>3.911342855487382</v>
+        <v>4.026845740679177</v>
       </c>
       <c r="J21" t="n">
         <v>62</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>3.670000076293945</v>
+        <v>3.625999927520752</v>
       </c>
       <c r="I22" t="n">
-        <v>5.994550284101392</v>
+        <v>6.067291902855144</v>
       </c>
       <c r="J22" t="n">
         <v>62</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>6.034999847412109</v>
+        <v>5.954999923706055</v>
       </c>
       <c r="I24" t="n">
-        <v>1.657000870395736</v>
+        <v>1.67926114661922</v>
       </c>
       <c r="J24" t="n">
         <v>62</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>4.09499979019165</v>
+        <v>4.005000114440918</v>
       </c>
       <c r="I26" t="n">
-        <v>2.930403080542865</v>
+        <v>2.996254596031429</v>
       </c>
       <c r="J26" t="n">
         <v>55</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2.660000085830688</v>
+        <v>2.720000028610229</v>
       </c>
       <c r="I28" t="n">
-        <v>5.639097562403148</v>
+        <v>5.514705824346692</v>
       </c>
       <c r="J28" t="n">
         <v>55</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>4.349999904632568</v>
+        <v>4.429999828338623</v>
       </c>
       <c r="I30" t="n">
-        <v>1.609195437578123</v>
+        <v>1.580135501410437</v>
       </c>
       <c r="J30" t="n">
         <v>48</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>31</v>
+        <v>30.45000076293945</v>
       </c>
       <c r="I31" t="n">
-        <v>0.4838709677419355</v>
+        <v>0.4926108250958215</v>
       </c>
       <c r="J31" t="n">
         <v>48</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>23.05999946594238</v>
+        <v>22.60000038146973</v>
       </c>
       <c r="I33" t="n">
-        <v>1.084128385905768</v>
+        <v>1.106194671593815</v>
       </c>
       <c r="J33" t="n">
         <v>34</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>31.85000038146973</v>
+        <v>31.89999961853027</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6122448906262828</v>
+        <v>0.6112852737676121</v>
       </c>
       <c r="J34" t="n">
         <v>34</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1.879999995231628</v>
+        <v>1.894999980926514</v>
       </c>
       <c r="I35" t="n">
-        <v>1.755319153388305</v>
+        <v>1.741424819638545</v>
       </c>
       <c r="J35" t="n">
         <v>34</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>5.070000171661377</v>
+        <v>5.059999942779541</v>
       </c>
       <c r="I36" t="n">
-        <v>5.719920910869921</v>
+        <v>5.731225361253625</v>
       </c>
       <c r="J36" t="n">
         <v>34</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>3.871999979019165</v>
+        <v>3.835999965667725</v>
       </c>
       <c r="I37" t="n">
-        <v>4.132231427349604</v>
+        <v>4.171011507612178</v>
       </c>
       <c r="J37" t="n">
         <v>34</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>2.706000089645386</v>
+        <v>2.697999954223633</v>
       </c>
       <c r="I38" t="n">
-        <v>5.121951049830274</v>
+        <v>5.137138708361582</v>
       </c>
       <c r="J38" t="n">
         <v>34</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>51.47000122070312</v>
+        <v>50.93000030517578</v>
       </c>
       <c r="I39" t="n">
-        <v>1.224013959701619</v>
+        <v>1.236991942322796</v>
       </c>
       <c r="J39" t="n">
         <v>34</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>5.260000228881836</v>
+        <v>5.239999771118164</v>
       </c>
       <c r="I40" t="n">
-        <v>2.661596842359093</v>
+        <v>2.67175584189244</v>
       </c>
       <c r="J40" t="n">
         <v>34</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>19</v>
+        <v>19.10000038146973</v>
       </c>
       <c r="I41" t="n">
-        <v>4.105263157894737</v>
+        <v>4.08376955194584</v>
       </c>
       <c r="J41" t="n">
         <v>34</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>24.75</v>
+        <v>24.55999946594238</v>
       </c>
       <c r="I42" t="n">
-        <v>3.434343434343434</v>
+        <v>3.460912127374856</v>
       </c>
       <c r="J42" t="n">
         <v>34</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>51.83000183105469</v>
+        <v>52.15000152587891</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1736446012357175</v>
+        <v>0.1725790937040307</v>
       </c>
       <c r="J43" t="n">
         <v>34</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1.25</v>
+        <v>1.230000019073486</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>0.8130081174740657</v>
       </c>
       <c r="J44" t="n">
         <v>34</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>6.349999904632568</v>
+        <v>6.309999942779541</v>
       </c>
       <c r="I45" t="n">
-        <v>2.855118153115793</v>
+        <v>2.873217141744343</v>
       </c>
       <c r="J45" t="n">
         <v>34</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>8.585000038146973</v>
+        <v>8.479999542236328</v>
       </c>
       <c r="I46" t="n">
-        <v>3.028538134475299</v>
+        <v>3.066037901358581</v>
       </c>
       <c r="J46" t="n">
         <v>34</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>9.925999641418457</v>
+        <v>9.87600040435791</v>
       </c>
       <c r="I47" t="n">
-        <v>2.790650916852298</v>
+        <v>2.80477914802201</v>
       </c>
       <c r="J47" t="n">
         <v>34</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1.169999957084656</v>
+        <v>1.159999966621399</v>
       </c>
       <c r="I48" t="n">
-        <v>1.15384619616898</v>
+        <v>1.163793136936023</v>
       </c>
       <c r="J48" t="n">
         <v>27</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>3.092000007629395</v>
+        <v>3.075999975204468</v>
       </c>
       <c r="I49" t="n">
-        <v>3.557567908427526</v>
+        <v>3.576072850673157</v>
       </c>
       <c r="J49" t="n">
         <v>27</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>3.150000095367432</v>
+        <v>3.089999914169312</v>
       </c>
       <c r="I51" t="n">
-        <v>5.079364925585401</v>
+        <v>5.177993671336816</v>
       </c>
       <c r="J51" t="n">
         <v>20</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0.9200000166893005</v>
+        <v>0.8500000238418579</v>
       </c>
       <c r="I52" t="n">
-        <v>2.71739125505287</v>
+        <v>2.94117638809046</v>
       </c>
       <c r="J52" t="n">
         <v>20</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>27.75</v>
+        <v>28.10000038146973</v>
       </c>
       <c r="I53" t="n">
-        <v>4</v>
+        <v>3.950177882317677</v>
       </c>
       <c r="J53" t="n">
         <v>16</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>0.890999972820282</v>
+        <v>0.875</v>
       </c>
       <c r="I54" t="n">
-        <v>3.367003469712912</v>
+        <v>3.428571428571429</v>
       </c>
       <c r="J54" t="n">
         <v>13</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.5059999823570251</v>
+        <v>0.5070000290870667</v>
       </c>
       <c r="I55" t="n">
-        <v>4.545454703943365</v>
+        <v>4.536488891611135</v>
       </c>
       <c r="J55" t="n">
         <v>13</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>19.89999961853027</v>
+        <v>20.10000038146973</v>
       </c>
       <c r="I56" t="n">
-        <v>3.015075434681407</v>
+        <v>2.985074570213155</v>
       </c>
       <c r="J56" t="n">
         <v>13</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>9</v>
+        <v>8.880000114440918</v>
       </c>
       <c r="I57" t="n">
-        <v>2.222222222222222</v>
+        <v>2.252252223226372</v>
       </c>
       <c r="J57" t="n">
         <v>13</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>2.535000085830688</v>
+        <v>2.505000114440918</v>
       </c>
       <c r="I58" t="n">
-        <v>7.100591475562661</v>
+        <v>7.185628414239556</v>
       </c>
       <c r="J58" t="n">
         <v>6</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>8.050000190734863</v>
+        <v>8.199999809265137</v>
       </c>
       <c r="I59" t="n">
-        <v>3.726707986234393</v>
+        <v>3.658536670464694</v>
       </c>
       <c r="J59" t="n">
         <v>6</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>14.39000034332275</v>
+        <v>14.31999969482422</v>
       </c>
       <c r="I60" t="n">
-        <v>1.737317540204264</v>
+        <v>1.745810093071156</v>
       </c>
       <c r="J60" t="n">
         <v>6</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>3.400000095367432</v>
+        <v>3.410000085830688</v>
       </c>
       <c r="I61" t="n">
-        <v>0.8823529164271378</v>
+        <v>0.8797653737504787</v>
       </c>
       <c r="J61" t="n">
         <v>6</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>13.60000038146973</v>
+        <v>14</v>
       </c>
       <c r="I63" t="n">
-        <v>4.264705762731166</v>
+        <v>4.142857142857142</v>
       </c>
       <c r="J63" t="n">
         <v>6</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>2.257999897003174</v>
+        <v>2.263000011444092</v>
       </c>
       <c r="I64" t="n">
-        <v>4.605846091402803</v>
+        <v>4.595669442071028</v>
       </c>
       <c r="J64" t="n">
         <v>-1</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>10.77499961853027</v>
+        <v>10.51500034332275</v>
       </c>
       <c r="I65" t="n">
-        <v>2.691415408509838</v>
+        <v>2.757964722123438</v>
       </c>
       <c r="J65" t="n">
         <v>-1</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>2.039999961853027</v>
+        <v>2.029999971389771</v>
       </c>
       <c r="I66" t="n">
-        <v>3.774509874503002</v>
+        <v>3.79310350173476</v>
       </c>
       <c r="J66" t="n">
         <v>-1</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>37.52500152587891</v>
+        <v>37.38000106811523</v>
       </c>
       <c r="I67" t="n">
-        <v>4.370419542472192</v>
+        <v>4.387372801331735</v>
       </c>
       <c r="J67" t="n">
         <v>-1</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>34.84000015258789</v>
+        <v>34.45000076293945</v>
       </c>
       <c r="I68" t="n">
-        <v>5.740528103446181</v>
+        <v>5.805515110906923</v>
       </c>
       <c r="J68" t="n">
         <v>-1</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>3.528000116348267</v>
+        <v>3.440000057220459</v>
       </c>
       <c r="I69" t="n">
-        <v>2.83446702670484</v>
+        <v>2.90697669583182</v>
       </c>
       <c r="J69" t="n">
         <v>-1</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>31.57999992370605</v>
+        <v>31.25</v>
       </c>
       <c r="I70" t="n">
-        <v>0.4701076642136279</v>
+        <v>0.475072</v>
       </c>
       <c r="J70" t="n">
         <v>-1</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>19.43000030517578</v>
+        <v>19.10000038146973</v>
       </c>
       <c r="I71" t="n">
-        <v>4.734945885486835</v>
+        <v>4.816753830500222</v>
       </c>
       <c r="J71" t="n">
         <v>-1</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>10.39999961853027</v>
+        <v>10.11999988555908</v>
       </c>
       <c r="I72" t="n">
-        <v>2.88461549042245</v>
+        <v>2.964426910993255</v>
       </c>
       <c r="J72" t="n">
         <v>-1</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>83.30000305175781</v>
+        <v>82</v>
       </c>
       <c r="I73" t="n">
-        <v>1.248499354020196</v>
+        <v>1.268292682926829</v>
       </c>
       <c r="J73" t="n">
         <v>-1</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>43.2599983215332</v>
+        <v>42.58000183105469</v>
       </c>
       <c r="I74" t="n">
-        <v>1.618123040128659</v>
+        <v>1.643964231794542</v>
       </c>
       <c r="J74" t="n">
         <v>-1</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>55.04999923706055</v>
+        <v>53.79999923706055</v>
       </c>
       <c r="I75" t="n">
-        <v>3.996366994531991</v>
+        <v>4.089219388844365</v>
       </c>
       <c r="J75" t="n">
         <v>-1</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>8.723999977111816</v>
+        <v>8.576999664306641</v>
       </c>
       <c r="I76" t="n">
-        <v>9.857863391291676</v>
+        <v>10.02681629543379</v>
       </c>
       <c r="J76" t="n">
         <v>-1</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>11.65200042724609</v>
+        <v>11.59799957275391</v>
       </c>
       <c r="I77" t="n">
-        <v>4.806041704998066</v>
+        <v>4.828418870746948</v>
       </c>
       <c r="J77" t="n">
         <v>-1</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>2.140000104904175</v>
+        <v>2.160000085830688</v>
       </c>
       <c r="I78" t="n">
-        <v>1.869158786877308</v>
+        <v>1.851851778265873</v>
       </c>
       <c r="J78" t="n">
         <v>-1</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>8.569999694824219</v>
+        <v>8.520000457763672</v>
       </c>
       <c r="I79" t="n">
-        <v>3.500583555226759</v>
+        <v>3.521126571379833</v>
       </c>
       <c r="J79" t="n">
         <v>-1</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>2.230000019073486</v>
+        <v>2.200000047683716</v>
       </c>
       <c r="I80" t="n">
-        <v>4.843049285931015</v>
+        <v>4.909090802689231</v>
       </c>
       <c r="J80" t="n">
         <v>-1</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>90.69999694824219</v>
+        <v>88</v>
       </c>
       <c r="I81" t="n">
-        <v>2.271223891193222</v>
+        <v>2.340909090909091</v>
       </c>
       <c r="J81" t="n">
         <v>-1</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>13.57999992370605</v>
+        <v>13.14999961853027</v>
       </c>
       <c r="I83" t="n">
-        <v>2.209131087521599</v>
+        <v>2.281368887473244</v>
       </c>
       <c r="J83" t="n">
         <v>-1</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I84" t="n">
-        <v>1.634615384615385</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="J84" t="n">
         <v>-1</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>35.7599983215332</v>
+        <v>35.31999969482422</v>
       </c>
       <c r="I85" t="n">
-        <v>2.376957605974396</v>
+        <v>2.406568537214791</v>
       </c>
       <c r="J85" t="n">
         <v>-1</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>70.41999816894531</v>
+        <v>69.69999694824219</v>
       </c>
       <c r="I86" t="n">
-        <v>1.846066506393762</v>
+        <v>1.865136380085287</v>
       </c>
       <c r="J86" t="n">
         <v>-1</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>7.460000038146973</v>
+        <v>7.440000057220459</v>
       </c>
       <c r="I87" t="n">
-        <v>8.04289540123162</v>
+        <v>8.064516067008695</v>
       </c>
       <c r="J87" t="n">
         <v>-1</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>5.730000019073486</v>
+        <v>5.570000171661377</v>
       </c>
       <c r="I89" t="n">
-        <v>3.490401384542038</v>
+        <v>3.590664162230099</v>
       </c>
       <c r="J89" t="n">
         <v>-1</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>23.36000061035156</v>
+        <v>23.02000045776367</v>
       </c>
       <c r="I90" t="n">
-        <v>4.280821805958635</v>
+        <v>4.344048566961441</v>
       </c>
       <c r="J90" t="n">
         <v>-1</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>4.5</v>
+        <v>4.489999771118164</v>
       </c>
       <c r="I91" t="n">
-        <v>4.777777777777778</v>
+        <v>4.788418952334548</v>
       </c>
       <c r="J91" t="n">
         <v>-1</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>23.97999954223633</v>
+        <v>23.86000061035156</v>
       </c>
       <c r="I92" t="n">
-        <v>1.125938303395065</v>
+        <v>1.131600976920603</v>
       </c>
       <c r="J92" t="n">
         <v>-1</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>9.760000228881836</v>
+        <v>9.420000076293945</v>
       </c>
       <c r="I93" t="n">
-        <v>2.04918027981351</v>
+        <v>2.123142233335149</v>
       </c>
       <c r="J93" t="n">
         <v>-1</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>8.244999885559082</v>
+        <v>8.060000419616699</v>
       </c>
       <c r="I94" t="n">
-        <v>2.910855104077736</v>
+        <v>2.977667338774325</v>
       </c>
       <c r="J94" t="n">
         <v>-1</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>21.04000091552734</v>
+        <v>20.6299991607666</v>
       </c>
       <c r="I95" t="n">
-        <v>3.754752688328006</v>
+        <v>3.829374852823038</v>
       </c>
       <c r="J95" t="n">
         <v>-1</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>5.239999771118164</v>
+        <v>5.199999809265137</v>
       </c>
       <c r="I96" t="n">
-        <v>1.774809237828549</v>
+        <v>1.788461604061919</v>
       </c>
       <c r="J96" t="n">
         <v>-1</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>6.599999904632568</v>
+        <v>6.900000095367432</v>
       </c>
       <c r="I97" t="n">
-        <v>0.909090922226919</v>
+        <v>0.8695652053727246</v>
       </c>
       <c r="J97" t="n">
         <v>-1</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>34.97999954223633</v>
+        <v>34.20000076293945</v>
       </c>
       <c r="I98" t="n">
-        <v>1.000571768382659</v>
+        <v>1.023391790035498</v>
       </c>
       <c r="J98" t="n">
         <v>-1</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>6.860000133514404</v>
+        <v>6.764999866485596</v>
       </c>
       <c r="I99" t="n">
-        <v>8.080174769851354</v>
+        <v>8.193643916329563</v>
       </c>
       <c r="J99" t="n">
         <v>-1</v>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>2.25</v>
+        <v>2.240000009536743</v>
       </c>
       <c r="I100" t="n">
-        <v>2.666666666666667</v>
+        <v>2.678571417167479</v>
       </c>
       <c r="J100" t="n">
         <v>-1</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>12.94999980926514</v>
+        <v>12.75</v>
       </c>
       <c r="I101" t="n">
-        <v>1.544401567148357</v>
+        <v>1.568627450980392</v>
       </c>
       <c r="J101" t="n">
         <v>-1</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>6.940000057220459</v>
+        <v>6.71999979019165</v>
       </c>
       <c r="I102" t="n">
-        <v>1.484149843670932</v>
+        <v>1.532738143092449</v>
       </c>
       <c r="J102" t="n">
         <v>-1</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>5.610000133514404</v>
+        <v>5.539000034332275</v>
       </c>
       <c r="I103" t="n">
-        <v>3.386809188558323</v>
+        <v>3.430222040482519</v>
       </c>
       <c r="J103" t="n">
         <v>-1</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>9.96399974822998</v>
+        <v>9.911999702453613</v>
       </c>
       <c r="I104" t="n">
-        <v>4.335608299034142</v>
+        <v>4.358353641728448</v>
       </c>
       <c r="J104" t="n">
         <v>-1</v>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>7.710000038146973</v>
+        <v>7.53000020980835</v>
       </c>
       <c r="I107" t="n">
-        <v>6.095979217568981</v>
+        <v>6.24169969328543</v>
       </c>
       <c r="J107" t="n">
         <v>-1</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>50.11999893188477</v>
+        <v>50.27999877929688</v>
       </c>
       <c r="I108" t="n">
-        <v>2.79329614891385</v>
+        <v>2.784407386613659</v>
       </c>
       <c r="J108" t="n">
         <v>-1</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>3.57699990272522</v>
+        <v>3.492000102996826</v>
       </c>
       <c r="I109" t="n">
-        <v>8.386916638477906</v>
+        <v>8.591065038702052</v>
       </c>
       <c r="J109" t="n">
         <v>-1</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>13.10000038146973</v>
+        <v>13.14999961853027</v>
       </c>
       <c r="I110" t="n">
-        <v>0.9160305076764956</v>
+        <v>0.9125475549892977</v>
       </c>
       <c r="J110" t="n">
         <v>-1</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>3.599999904632568</v>
+        <v>3.450000047683716</v>
       </c>
       <c r="I111" t="n">
-        <v>4.722222347318394</v>
+        <v>4.927536163778773</v>
       </c>
       <c r="J111" t="n">
         <v>-1</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>22.04999923706055</v>
+        <v>21.89999961853027</v>
       </c>
       <c r="I112" t="n">
-        <v>3.174603284445809</v>
+        <v>3.19634708763971</v>
       </c>
       <c r="J112" t="n">
         <v>-1</v>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>2.380000114440918</v>
+        <v>2.359999895095825</v>
       </c>
       <c r="I113" t="n">
-        <v>1.47058816458174</v>
+        <v>1.483050913380607</v>
       </c>
       <c r="J113" t="n">
         <v>-1</v>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>5.679999828338623</v>
+        <v>5.579999923706055</v>
       </c>
       <c r="I114" t="n">
-        <v>5.809859330515573</v>
+        <v>5.913978575484007</v>
       </c>
       <c r="J114" t="n">
         <v>-1</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>0.8920000195503235</v>
+        <v>0.8899999856948853</v>
       </c>
       <c r="I115" t="n">
-        <v>7.847533460289442</v>
+        <v>7.865168665743978</v>
       </c>
       <c r="J115" t="n">
         <v>-1</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>50.90000152587891</v>
+        <v>50.95000076293945</v>
       </c>
       <c r="I116" t="n">
-        <v>1.394891903174143</v>
+        <v>1.393523040958318</v>
       </c>
       <c r="J116" t="n">
         <v>-1</v>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>104.5999984741211</v>
+        <v>103.5999984741211</v>
       </c>
       <c r="I117" t="n">
-        <v>1.290630993970809</v>
+        <v>1.303088822281426</v>
       </c>
       <c r="J117" t="n">
         <v>-1</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>7.019999980926514</v>
+        <v>7.28000020980835</v>
       </c>
       <c r="I118" t="n">
-        <v>1.13960114269746</v>
+        <v>1.098901067230959</v>
       </c>
       <c r="J118" t="n">
         <v>-1</v>
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>4.559999942779541</v>
+        <v>4.447000026702881</v>
       </c>
       <c r="I120" t="n">
-        <v>3.728070222219713</v>
+        <v>3.822801865959113</v>
       </c>
       <c r="J120" t="n">
         <v>-1</v>
@@ -6163,10 +6163,10 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>58.59999847412109</v>
+        <v>57.09999847412109</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7679181087329359</v>
+        <v>0.7880910893613235</v>
       </c>
       <c r="J122" t="n">
         <v>-1</v>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.179999828338623</v>
+        <v>5.5</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7722007977909368</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="J123" t="n">
         <v>-1</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>37.29999923706055</v>
+        <v>36</v>
       </c>
       <c r="I124" t="n">
-        <v>2.815013462404419</v>
+        <v>2.916666666666667</v>
       </c>
       <c r="J124" t="n">
         <v>-1</v>
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>20.86000061035156</v>
+        <v>20.68000030517578</v>
       </c>
       <c r="I126" t="n">
-        <v>1.821668211320324</v>
+        <v>1.837524150833275</v>
       </c>
       <c r="J126" t="n">
         <v>-1</v>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>25.96999931335449</v>
+        <v>25.89999961853027</v>
       </c>
       <c r="I127" t="n">
-        <v>2.310358166592108</v>
+        <v>2.316602350722535</v>
       </c>
       <c r="J127" t="n">
         <v>-1</v>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>36.5</v>
+        <v>35.65000152587891</v>
       </c>
       <c r="I128" t="n">
-        <v>0.9589041095890409</v>
+        <v>0.9817671389044105</v>
       </c>
       <c r="J128" t="n">
         <v>-1</v>
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>3.5</v>
+        <v>3.299999952316284</v>
       </c>
       <c r="I129" t="n">
-        <v>0.4857142857142858</v>
+        <v>0.5151515225952542</v>
       </c>
       <c r="J129" t="n">
         <v>-1</v>
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>21.29999923706055</v>
+        <v>21.17000007629395</v>
       </c>
       <c r="I131" t="n">
-        <v>5.258216150784064</v>
+        <v>5.290505413149101</v>
       </c>
       <c r="J131" t="n">
         <v>-1</v>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>1.460000038146973</v>
+        <v>1.480000019073486</v>
       </c>
       <c r="I132" t="n">
-        <v>6.849314889533817</v>
+        <v>6.756756669679118</v>
       </c>
       <c r="J132" t="n">
         <v>-1</v>
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>2.539999961853027</v>
+        <v>2.440000057220459</v>
       </c>
       <c r="I133" t="n">
-        <v>10.23622062617356</v>
+        <v>10.65573745503025</v>
       </c>
       <c r="J133" t="n">
         <v>-1</v>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>2.148000001907349</v>
+        <v>2.099999904632568</v>
       </c>
       <c r="I134" t="n">
-        <v>4.297020480355719</v>
+        <v>4.395238294839327</v>
       </c>
       <c r="J134" t="n">
         <v>-1</v>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>8.699999809265137</v>
+        <v>8.899999618530273</v>
       </c>
       <c r="I135" t="n">
-        <v>4.022988593945308</v>
+        <v>3.932584438220439</v>
       </c>
       <c r="J135" t="n">
         <v>-8</v>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>5.199999809265137</v>
+        <v>5.300000190734863</v>
       </c>
       <c r="I136" t="n">
-        <v>1.846153913870368</v>
+        <v>1.811320689531697</v>
       </c>
       <c r="J136" t="n">
         <v>-8</v>
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>9.399999618530273</v>
+        <v>9.5</v>
       </c>
       <c r="I139" t="n">
-        <v>0.6382978982437579</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="J139" t="n">
         <v>-8</v>
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>15.31999969482422</v>
+        <v>15.18000030517578</v>
       </c>
       <c r="I142" t="n">
-        <v>3.263707636814917</v>
+        <v>3.293807575415659</v>
       </c>
       <c r="J142" t="n">
         <v>-8</v>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>3.700000047683716</v>
+        <v>3.720000028610229</v>
       </c>
       <c r="I143" t="n">
-        <v>2.702702667871647</v>
+        <v>2.688172022336232</v>
       </c>
       <c r="J143" t="n">
         <v>-8</v>
@@ -7197,10 +7197,10 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>3.789999961853027</v>
+        <v>3.680000066757202</v>
       </c>
       <c r="I144" t="n">
-        <v>2.902374699397575</v>
+        <v>2.989130380558157</v>
       </c>
       <c r="J144" t="n">
         <v>-8</v>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>8.899999618530273</v>
+        <v>9.149999618530273</v>
       </c>
       <c r="I145" t="n">
-        <v>0.9550562207106782</v>
+        <v>0.9289617873629289</v>
       </c>
       <c r="J145" t="n">
         <v>-8</v>
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>4.809999942779541</v>
+        <v>4.739999771118164</v>
       </c>
       <c r="I146" t="n">
-        <v>1.975051998547481</v>
+        <v>2.004219506061063</v>
       </c>
       <c r="J146" t="n">
         <v>-8</v>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>7.849999904632568</v>
+        <v>8.100000381469727</v>
       </c>
       <c r="I148" t="n">
-        <v>1.14649682921509</v>
+        <v>1.111111058783305</v>
       </c>
       <c r="J148" t="n">
         <v>-8</v>
@@ -7479,10 +7479,10 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>7.03000020980835</v>
+        <v>6.949999809265137</v>
       </c>
       <c r="I150" t="n">
-        <v>3.129445141310993</v>
+        <v>3.16546771277195</v>
       </c>
       <c r="J150" t="n">
         <v>-8</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>28.75</v>
+        <v>27.70000076293945</v>
       </c>
       <c r="I151" t="n">
-        <v>2.121739130434783</v>
+        <v>2.202166004327822</v>
       </c>
       <c r="J151" t="n">
         <v>-15</v>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>2.740000009536743</v>
+        <v>2.730000019073486</v>
       </c>
       <c r="I152" t="n">
-        <v>5.474452535690348</v>
+        <v>5.494505456117444</v>
       </c>
       <c r="J152" t="n">
         <v>-15</v>
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>8.699999809265137</v>
+        <v>8.609999656677246</v>
       </c>
       <c r="I154" t="n">
-        <v>5.86781622059737</v>
+        <v>5.929152385088609</v>
       </c>
       <c r="J154" t="n">
         <v>-15</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>8.524999618530273</v>
+        <v>8.449999809265137</v>
       </c>
       <c r="I155" t="n">
-        <v>3.167155566941228</v>
+        <v>3.195266344313455</v>
       </c>
       <c r="J155" t="n">
         <v>-15</v>
@@ -7761,10 +7761,10 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>6.920000076293945</v>
+        <v>6.664999961853027</v>
       </c>
       <c r="I156" t="n">
-        <v>5.057803412445119</v>
+        <v>5.251312858262819</v>
       </c>
       <c r="J156" t="n">
         <v>-15</v>
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>10.39999961853027</v>
+        <v>10</v>
       </c>
       <c r="I159" t="n">
-        <v>4.134615536272179</v>
+        <v>4.3</v>
       </c>
       <c r="J159" t="n">
         <v>-15</v>
@@ -7996,10 +7996,10 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>12.10000038146973</v>
+        <v>11.97999954223633</v>
       </c>
       <c r="I161" t="n">
-        <v>1.629495816396419</v>
+        <v>1.645818092937874</v>
       </c>
       <c r="J161" t="n">
         <v>-15</v>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>28.29999923706055</v>
+        <v>28.60000038146973</v>
       </c>
       <c r="I162" t="n">
-        <v>3.886925899840606</v>
+        <v>3.846153794853453</v>
       </c>
       <c r="J162" t="n">
         <v>-15</v>
@@ -8090,10 +8090,10 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>66</v>
+        <v>65.09999847412109</v>
       </c>
       <c r="I163" t="n">
-        <v>0.7121212121212122</v>
+        <v>0.7219662227593399</v>
       </c>
       <c r="J163" t="n">
         <v>-15</v>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>89.90000152587891</v>
+        <v>87</v>
       </c>
       <c r="I164" t="n">
-        <v>1.334816440080442</v>
+        <v>1.379310344827586</v>
       </c>
       <c r="J164" t="n">
         <v>-15</v>
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>22.54999923706055</v>
+        <v>22.39999961853027</v>
       </c>
       <c r="I165" t="n">
-        <v>1.197339286629596</v>
+        <v>1.205357163384253</v>
       </c>
       <c r="J165" t="n">
         <v>-15</v>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>34.25</v>
+        <v>33.29999923706055</v>
       </c>
       <c r="I167" t="n">
-        <v>0.875912408759124</v>
+        <v>0.9009009215415272</v>
       </c>
       <c r="J167" t="n">
         <v>-15</v>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>0.1659999936819077</v>
+        <v>0.1710000038146973</v>
       </c>
       <c r="I168" t="n">
-        <v>4.216867630376862</v>
+        <v>4.093567160141991</v>
       </c>
       <c r="J168" t="n">
         <v>-22</v>
@@ -8372,10 +8372,10 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>6.820000171661377</v>
+        <v>6.730000019073486</v>
       </c>
       <c r="I169" t="n">
-        <v>2.346040996667943</v>
+        <v>2.377414554926362</v>
       </c>
       <c r="J169" t="n">
         <v>-22</v>
@@ -8466,10 +8466,10 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>8.439999580383301</v>
+        <v>8.220000267028809</v>
       </c>
       <c r="I171" t="n">
-        <v>2.962085455324706</v>
+        <v>3.041362431614187</v>
       </c>
       <c r="J171" t="n">
         <v>-22</v>
@@ -8560,10 +8560,10 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>7.239999771118164</v>
+        <v>7.159999847412109</v>
       </c>
       <c r="I173" t="n">
-        <v>6.906077566391673</v>
+        <v>6.983240372284626</v>
       </c>
       <c r="J173" t="n">
         <v>-29</v>
@@ -8607,10 +8607,10 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>19.21999931335449</v>
+        <v>19.02000045776367</v>
       </c>
       <c r="I174" t="n">
-        <v>3.381893981382014</v>
+        <v>3.417455227950218</v>
       </c>
       <c r="J174" t="n">
         <v>-29</v>
@@ -8654,10 +8654,10 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>13.0600004196167</v>
+        <v>12.86999988555908</v>
       </c>
       <c r="I175" t="n">
-        <v>4.134762501147367</v>
+        <v>4.195804233113574</v>
       </c>
       <c r="J175" t="n">
         <v>-29</v>
@@ -8701,10 +8701,10 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>5.486000061035156</v>
+        <v>5.519999980926514</v>
       </c>
       <c r="I176" t="n">
-        <v>1.822821707754975</v>
+        <v>1.811594209158228</v>
       </c>
       <c r="J176" t="n">
         <v>-29</v>
@@ -8748,10 +8748,10 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>8.199999809265137</v>
+        <v>8.300000190734863</v>
       </c>
       <c r="I177" t="n">
-        <v>1.95121955758117</v>
+        <v>1.927710799074499</v>
       </c>
       <c r="J177" t="n">
         <v>-29</v>
@@ -8795,10 +8795,10 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>283.2999877929688</v>
+        <v>286.6000061035156</v>
       </c>
       <c r="I178" t="n">
-        <v>1.276032529391348</v>
+        <v>1.261339819614071</v>
       </c>
       <c r="J178" t="n">
         <v>-29</v>
@@ -8842,10 +8842,10 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>28.5</v>
+        <v>27.5</v>
       </c>
       <c r="I179" t="n">
-        <v>4.771929824561403</v>
+        <v>4.945454545454546</v>
       </c>
       <c r="J179" t="n">
         <v>-29</v>
@@ -8889,10 +8889,10 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>13.90999984741211</v>
+        <v>13.92000007629395</v>
       </c>
       <c r="I180" t="n">
-        <v>41.85190556334249</v>
+        <v>41.821838851239</v>
       </c>
       <c r="J180" t="n">
         <v>-29</v>
@@ -8936,10 +8936,10 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>14.06999969482422</v>
+        <v>14.03999996185303</v>
       </c>
       <c r="I181" t="n">
-        <v>4.157782606173031</v>
+        <v>4.166666677987586</v>
       </c>
       <c r="J181" t="n">
         <v>-29</v>
@@ -8983,10 +8983,10 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>21.05999946594238</v>
+        <v>20.60000038146973</v>
       </c>
       <c r="I182" t="n">
-        <v>2.991453067312835</v>
+        <v>3.058252370551908</v>
       </c>
       <c r="J182" t="n">
         <v>-29</v>
@@ -9030,10 +9030,10 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>143.0500030517578</v>
+        <v>140.5</v>
       </c>
       <c r="I183" t="n">
-        <v>0.6291506332050657</v>
+        <v>0.6405693950177936</v>
       </c>
       <c r="J183" t="n">
         <v>-29</v>
@@ -9077,10 +9077,10 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>70.94000244140625</v>
+        <v>70.45999908447266</v>
       </c>
       <c r="I184" t="n">
-        <v>2.425711785704145</v>
+        <v>2.442236761792997</v>
       </c>
       <c r="J184" t="n">
         <v>-29</v>
@@ -11303,146 +11303,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Cementir Holding N.V.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Cementir Holding N.V.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Cementir Holding N.V.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>DHH S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Ferretti S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>OMER S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>TESMEC S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>